--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487917_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487917_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2103</v>
+        <v>3.4457</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3585</v>
+        <v>2.6887</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8518</v>
+        <v>0.757</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.288</v>
+        <v>1.9135</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.062</v>
+        <v>-0.6501</v>
       </c>
       <c r="I2" t="n">
-        <v>0.774</v>
+        <v>2.5636</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3242</v>
+        <v>2.3506</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5593</v>
+        <v>0.1831</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2351</v>
+        <v>2.1676</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9638</v>
+        <v>-0.4371</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5026</v>
+        <v>-0.8331</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5389</v>
+        <v>0.396</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6845</v>
+        <v>-0.1328</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9283</v>
+        <v>-0.2457</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7562</v>
+        <v>0.1129</v>
       </c>
       <c r="V2" t="n">
-        <v>2.565</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.795</v>
+        <v>0.5838</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.23</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6494</v>
+        <v>3.1819</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9805</v>
+        <v>1.8879</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6689000000000001</v>
+        <v>1.294</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9135</v>
+        <v>-1.288</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6501</v>
+        <v>-2.062</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5636</v>
+        <v>0.774</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3506</v>
+        <v>-0.3242</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1831</v>
+        <v>-0.5593</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1676</v>
+        <v>0.2351</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4371</v>
+        <v>-0.9638</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8331</v>
+        <v>-1.5026</v>
       </c>
       <c r="O3" t="n">
-        <v>0.396</v>
+        <v>0.5389</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.929</v>
+        <v>0.6562</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9539</v>
+        <v>0.4577</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0249</v>
+        <v>0.1984</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.565</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5838</v>
+        <v>2.795</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1746</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4438</v>
+        <v>-0.551</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.501</v>
       </c>
       <c r="G4" t="n">
         <v>0.216</v>
@@ -766,13 +766,13 @@
         <v>0.6244</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2479</v>
+        <v>0.0233</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2048</v>
+        <v>0.0977</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0431</v>
+        <v>-0.0743</v>
       </c>
       <c r="V4" t="n">
         <v>1.1675</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2349</v>
+        <v>-0.3332</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1903</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0446</v>
+        <v>-0.2501</v>
       </c>
       <c r="G5" t="n">
         <v>-1.8281</v>
@@ -844,13 +844,13 @@
         <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7607</v>
+        <v>0.6623</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0619</v>
+        <v>0.1691</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6988</v>
+        <v>0.4932</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3985</v>
+        <v>-0.796</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.902</v>
+        <v>-1.6225</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.8265</v>
       </c>
       <c r="G6" t="n">
         <v>-2.688</v>
@@ -922,13 +922,13 @@
         <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9186</v>
+        <v>-0.3161</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3047</v>
+        <v>-0.0252</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6139</v>
+        <v>-0.2909</v>
       </c>
       <c r="V6" t="n">
         <v>1.1675</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6628</v>
+        <v>-1.7905</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6233</v>
+        <v>-1.5162</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0395</v>
+        <v>-0.2744</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7917</v>
@@ -1000,13 +1000,13 @@
         <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4143</v>
+        <v>-0.542</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3791</v>
+        <v>-0.2719</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0352</v>
+        <v>-0.2701</v>
       </c>
       <c r="V7" t="n">
         <v>1.1675</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7127</v>
+        <v>-2.2103</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5085</v>
+        <v>-1.8299</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2042</v>
+        <v>-0.3804</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0273</v>
@@ -1078,13 +1078,13 @@
         <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>0.274</v>
+        <v>-0.2236</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.2748</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3223</v>
+        <v>-0.4984</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5838</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8697</v>
+        <v>-2.5024</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.801</v>
+        <v>-2.5511</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0687</v>
+        <v>0.0487</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0506</v>
@@ -1156,13 +1156,13 @@
         <v>0.2081</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9727</v>
+        <v>0.3401</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0373</v>
+        <v>0.2872</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0646</v>
+        <v>0.0529</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>A. RODRIGUEZ MONTON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0775</v>
+        <v>-3.0936</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4724</v>
+        <v>-2.7909</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3949</v>
+        <v>-0.3027</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2684</v>
+        <v>-2.0033</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6416</v>
+        <v>-2.2409</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3732</v>
+        <v>0.2376</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4151</v>
+        <v>-0.705</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5719</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1568</v>
+        <v>-0.0482</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1467</v>
+        <v>-1.2983</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0697</v>
+        <v>-1.5841</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2165</v>
+        <v>0.2857</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.3299</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.2029</v>
+        <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2929</v>
+        <v>-0.0498</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7482</v>
+        <v>-0.0047</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0412</v>
+        <v>-0.045</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ MONTON</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4738</v>
+        <v>-3.2838</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1124</v>
+        <v>-4.9429</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3615</v>
+        <v>1.6591</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0033</v>
+        <v>-0.2684</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2409</v>
+        <v>-1.6416</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2376</v>
+        <v>1.3732</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.705</v>
+        <v>-1.4151</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-1.5719</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0482</v>
+        <v>0.1568</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2983</v>
+        <v>1.1467</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5841</v>
+        <v>-0.0697</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2857</v>
+        <v>1.2165</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0406</v>
+        <v>-3.3299</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0812</v>
+        <v>-5.2029</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4299</v>
+        <v>-0.4992</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3262</v>
+        <v>0.2777</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1037</v>
+        <v>-0.7769</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7438</v>
+        <v>-3.3809</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2375</v>
+        <v>-5.315</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4937</v>
+        <v>1.9341</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8401999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3219</v>
+        <v>-0.959</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.072</v>
+        <v>-0.1495</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2499</v>
+        <v>-0.8096</v>
       </c>
       <c r="V12" t="n">
         <v>0.7076</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.1394</v>
+        <v>-10.8131</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.9522</v>
+        <v>-16.626</v>
       </c>
       <c r="F13" t="n">
-        <v>5.8127</v>
+        <v>5.8128</v>
       </c>
       <c r="G13" t="n">
         <v>-13.6561</v>
@@ -1444,7 +1444,7 @@
         <v>-9.122399999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.162699999999999</v>
+        <v>-5.1627</v>
       </c>
       <c r="L13" t="n">
         <v>-3.9597</v>
@@ -1456,7 +1456,7 @@
         <v>-4.921400000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3879999999999999</v>
+        <v>0.388</v>
       </c>
       <c r="P13" t="n">
         <v>-3.1218</v>
@@ -1468,10 +1468,10 @@
         <v>13.5278</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3668</v>
+        <v>-1.0406</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5409000000000002</v>
+        <v>0.8672</v>
       </c>
       <c r="U13" t="n">
         <v>-1.9078</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.4108</v>
+        <v>8.5276</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3364</v>
+        <v>5.0149</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0744</v>
+        <v>3.5126</v>
       </c>
       <c r="G14" t="n">
         <v>7.6215</v>
@@ -1546,13 +1546,13 @@
         <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7081</v>
+        <v>0.8248</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3601</v>
+        <v>0.0386</v>
       </c>
       <c r="U14" t="n">
-        <v>1.348</v>
+        <v>0.7862</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1675</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5884</v>
+        <v>4.9162</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0914</v>
+        <v>2.3057</v>
       </c>
       <c r="F15" t="n">
-        <v>2.497</v>
+        <v>2.6105</v>
       </c>
       <c r="G15" t="n">
         <v>3.0206</v>
@@ -1624,13 +1624,13 @@
         <v>2.2893</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9029</v>
+        <v>1.2307</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4501</v>
+        <v>0.6644</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4528</v>
+        <v>0.5663</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5838</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7537</v>
+        <v>4.0641</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5903</v>
+        <v>3.2332</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1635</v>
+        <v>0.8309</v>
       </c>
       <c r="G16" t="n">
         <v>4.5275</v>
@@ -1702,13 +1702,13 @@
         <v>1.6649</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8143</v>
+        <v>-0.504</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.2457</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9257</v>
+        <v>-0.2583</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5838</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2371</v>
+        <v>2.0013</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.1464</v>
+        <v>-2.9321</v>
       </c>
       <c r="F17" t="n">
-        <v>4.3835</v>
+        <v>4.9335</v>
       </c>
       <c r="G17" t="n">
         <v>1.7685</v>
@@ -1780,13 +1780,13 @@
         <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4482</v>
+        <v>0.3161</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1338</v>
+        <v>0.0805</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3144</v>
+        <v>0.2356</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7076</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9307</v>
+        <v>1.6999</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1011</v>
+        <v>-1.6724</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0318</v>
+        <v>3.3723</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6385</v>
@@ -1858,13 +1858,13 @@
         <v>2.4974</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0718</v>
+        <v>0.8409</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0314</v>
+        <v>0.3972</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1031</v>
+        <v>0.4437</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.185</v>
+        <v>0.2437</v>
       </c>
       <c r="E19" t="n">
         <v>0.4011</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2161</v>
+        <v>-0.1574</v>
       </c>
       <c r="G19" t="n">
         <v>1.1271</v>
@@ -1936,13 +1936,13 @@
         <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.169</v>
+        <v>-0.1103</v>
       </c>
       <c r="T19" t="n">
         <v>-0.171</v>
       </c>
       <c r="U19" t="n">
-        <v>0.002</v>
+        <v>0.0607</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3975</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1379</v>
+        <v>0.0958</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8212</v>
+        <v>0.6069</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6833</v>
+        <v>-0.5111</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5184</v>
@@ -2014,13 +2014,13 @@
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1762</v>
+        <v>-0.2182</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1924</v>
+        <v>-0.0219</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3686</v>
+        <v>-0.1964</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0898</v>
+        <v>-0.3665</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9984</v>
+        <v>-0.8794</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9086</v>
+        <v>0.5129</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.032</v>
+        <v>-1.3882</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.143</v>
+        <v>1.4946</v>
       </c>
       <c r="I21" t="n">
-        <v>0.111</v>
+        <v>-2.8828</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3584</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4693</v>
+        <v>1.1233</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8891</v>
+        <v>-1.8174</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3265</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6737</v>
+        <v>0.3713</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0001</v>
+        <v>-1.0654</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3178</v>
+        <v>-0.1864</v>
       </c>
       <c r="T21" t="n">
-        <v>1.4007</v>
+        <v>0.2715</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0828</v>
+        <v>-0.4579</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5838</v>
+        <v>0.5838</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3641</v>
+        <v>-0.5605</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-1.6413</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1939</v>
+        <v>1.0808</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3882</v>
+        <v>-1.032</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4946</v>
+        <v>-1.143</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8828</v>
+        <v>0.111</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-1.3584</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1233</v>
+        <v>-0.4693</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.8174</v>
+        <v>-0.8891</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6941000000000001</v>
+        <v>0.3265</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3713</v>
+        <v>-0.6737</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0654</v>
+        <v>1.0001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.184</v>
+        <v>0.8471</v>
       </c>
       <c r="T22" t="n">
-        <v>0.593</v>
+        <v>0.7577</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.777</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5838</v>
+        <v>-0.5838</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1593</v>
+        <v>-1.3481</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3121</v>
+        <v>-3.5264</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1529</v>
+        <v>2.1783</v>
       </c>
       <c r="G23" t="n">
         <v>0.2947</v>
@@ -2248,13 +2248,13 @@
         <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1704</v>
+        <v>0.9815</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6987</v>
+        <v>0.4844</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4717</v>
+        <v>0.4972</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1675</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.491</v>
+        <v>-5.991</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.9371</v>
+        <v>-6.7228</v>
       </c>
       <c r="F24" t="n">
-        <v>0.446</v>
+        <v>0.7318</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1268</v>
@@ -2326,13 +2326,13 @@
         <v>1.2487</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0125</v>
+        <v>-0.5125</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5624</v>
+        <v>-0.3481</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4501</v>
+        <v>-0.1643</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3975</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>11.1394</v>
+        <v>13.2825</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.8127</v>
+        <v>-5.812600000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>16.9522</v>
+        <v>19.0951</v>
       </c>
       <c r="G25" t="n">
         <v>13.656</v>
@@ -2374,16 +2374,16 @@
         <v>10.0842</v>
       </c>
       <c r="I25" t="n">
-        <v>3.5719</v>
+        <v>3.571900000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>4.533500000000002</v>
+        <v>4.5335</v>
       </c>
       <c r="K25" t="n">
-        <v>4.921500000000001</v>
+        <v>4.9215</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3878</v>
+        <v>-0.3877999999999998</v>
       </c>
       <c r="M25" t="n">
         <v>9.1225</v>
@@ -2404,13 +2404,13 @@
         <v>16.6493</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3668</v>
+        <v>3.5097</v>
       </c>
       <c r="T25" t="n">
-        <v>1.9078</v>
+        <v>1.9076</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5409999999999997</v>
+        <v>1.6022</v>
       </c>
       <c r="V25" t="n">
         <v>-7.005199999999999</v>
